--- a/sample_data/demo/고객명단.xlsx
+++ b/sample_data/demo/고객명단.xlsx
@@ -7,17 +7,24 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고객명단" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고객 현황" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="운영 요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="열람 안내" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'고객 현황'!$A$5:$H$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'고객 현황'!$1:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +32,101 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00202B33"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="00667380"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00202B33"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="008A5A00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000D6754"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="0017324D"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00202B33"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="0017324D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00202B33"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017324D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDF3EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +134,79 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D8DEE6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -410,173 +569,1346 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0017324D"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026년 3분기 고객 관리 현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>고객경험팀 내부 검토용  |  기준일 2026-09-13  |  합성 데모 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>고객 ID</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>고객명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>가입일</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>BW-260301</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>배병철</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>010-2310-6710</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>customer.01@example.com</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>전라남도 수원시 장안구 삼성5가 706-18</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>46085</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>김하늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="31" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>BW-260302</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>김명숙</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>010-2311-6711</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>customer.02@example.com</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>충청북도 춘천시 선릉4로 539 (현준김마을)</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>46096</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="31" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>BW-260303</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>김수진</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>010-2312-6712</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>customer.03@example.com</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>세종특별자치시 강서구 삼성8길 451-99 (성수김윤읍)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>46107</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="31" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>BW-260304</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>임건우</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>우수</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>010-2313-6713</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>customer.04@example.com</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>전북특별자치도 용인시 기흥구 서초대가 893</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>46118</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>김하늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="31" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>BW-260305</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>류선영</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>010-2314-6714</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>customer.05@example.com</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>서울특별시 금천구 봉은사로 579-79</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>46129</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="31" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>BW-260306</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>김미정</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>010-2315-6715</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>customer.06@example.com</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>부산광역시 서대문구 반포대3가 287</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>46140</v>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="31" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>BW-260307</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>김영일</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>우수</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>010-2316-6716</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>customer.07@example.com</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>인천광역시 동대문구 봉은사로 980</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>46151</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>김하늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="31" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>BW-260308</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>엄유진</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>010-2317-6717</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>customer.08@example.com</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>대구광역시 강남구 석촌호수4거리 772</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>46162</v>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="31" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>BW-260309</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>김하윤</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>우수</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>010-2318-6718</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>customer.09@example.com</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>제주특별자치도 청주시 청원구 테헤란가 467-57</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="31" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>BW-260310</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>이경수</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>010-2319-6719</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>customer.10@example.com</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>울산광역시 금천구 압구정길 441-18 (중수주읍)</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>46184</v>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>김하늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="31" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BW-260311</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>김선영</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>010-2320-6720</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>customer.11@example.com</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>충청북도 김포시 양재천거리 377 (정순김리)</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>46195</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="31" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>BW-260312</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>김옥순</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>010-2321-6721</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>customer.12@example.com</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>경상남도 보은군 압구정거리 328</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>46206</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="31" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BW-260313</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>박성훈</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>010-2322-6722</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>customer.13@example.com</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>경상북도 양구군 반포대로 993 (현준정마을)</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>46217</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>김하늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="31" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>BW-260314</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>강수빈</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>우수</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>010-2323-6723</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>customer.14@example.com</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>충청북도 부여군 강남대8가 지하984 (미정이윤리)</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>46228</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="31" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BW-260315</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>황상호</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>010-2324-6724</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>customer.15@example.com</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>광주광역시 송파구 개포길 834 (진우하동)</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="31" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>BW-260316</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>이재현</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>010-2325-6725</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>customer.16@example.com</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>강원특별자치도 안양시 만안구 강남대706거리 지하459 (진호김황마을)</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>46250</v>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>김하늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="31" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>BW-260317</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>김영길</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>우수</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>010-2326-6726</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>customer.17@example.com</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>세종특별자치시 강남구 봉은사7로 지하987</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>46261</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="31" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>BW-260318</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>김건우</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>010-2327-6727</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>customer.18@example.com</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>인천광역시 중랑구 영동대71가 999-10 (상철박마을)</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>46272</v>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="31" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>BW-260319</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>윤경희</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>우수</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>010-2328-6728</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>customer.19@example.com</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>대전광역시 성북구 봉은사거리 321-55</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>46283</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>김하늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="31" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>BW-260320</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>박예지</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>010-2329-6729</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>customer.20@example.com</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>부산광역시 중랑구 가락83길 975</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="31" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BW-260321</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>김승민</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>010-2330-6730</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>customer.21@example.com</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>인천광역시 도봉구 백제고분로 527 (경수이동)</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>46305</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="31" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>BW-260322</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>김채원</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>010-2331-6731</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>customer.22@example.com</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>부산광역시 종로구 오금2거리 199 (경희정마을)</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>46316</v>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>김하늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="31" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BW-260323</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>김정순</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>010-2332-6732</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>customer.23@example.com</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>부산광역시 도봉구 논현거리 612 (지우김한리)</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>46327</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="31" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>BW-260324</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>심상훈</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>우수</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>010-2333-6733</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>customer.24@example.com</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>대전광역시 강북구 논현가 546</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>46338</v>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:H29"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C블루웨이브 솔루션  |  합성 데모 문서&amp;RPage &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002D6CDF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>고객명</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>이메일</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>주소</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>고객 운영 요약</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>배병철</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>010-1201-5601</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>demo.user1@example.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>전라남도 수원시 장안구 삼성5가 706-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>김명숙</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>010-1202-5602</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>demo.user2@example.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>충청북도 춘천시 선릉4로 539 (현준김마을)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>김수진</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>010-1203-5603</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>demo.user3@example.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>세종특별자치시 강서구 삼성8길 451-99 (성수김윤읍)</t>
-        </is>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>전체 고객</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>임건우</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>010-1204-5604</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>demo.user4@example.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>전북특별자치도 용인시 기흥구 서초대가 893</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>류선영</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>010-1205-5605</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>demo.user5@example.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>서울특별시 금천구 봉은사로 579-79</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>김미정</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>010-1206-5606</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>demo.user6@example.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>부산광역시 서대문구 반포대3가 287</t>
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>관리 고객</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>우수</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>검토 상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>김하늘</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>검토 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>검토 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>확인 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>등급별 운영 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>월 1회 담당자 확인</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>우선 응대</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>우수</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>분기 1회 정보 갱신</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>일반 응대</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>반기 1회 정보 갱신</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>일반 응대</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00138A72"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>고객정보 취급 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>문서 목적</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>InfoGuard의 개인정보 탐지와 마스킹 기능을 시연하기 위한 합성 고객명단</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>취급 등급</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>내부 검토용</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>포함 정보</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>합성 이름, 연락처, 이메일, 주소</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>주의 사항</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>실제 고객정보가 아니며 외부 업무에 사용할 수 없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sample_data/demo/고객명단.xlsx
+++ b/sample_data/demo/고객명단.xlsx
@@ -10,10 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고객 현황" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="운영 요약" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="열람 안내" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="탐지 비교" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'고객 현황'!$A$5:$H$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'고객 현황'!$1:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'탐지 비교'!$A$4:$D$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'탐지 비교'!$A$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -143,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -206,6 +209,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1911,4 +1920,353 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D9822B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>개인정보 탐지와 오탐 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>동일한 번호 형식도 문맥에 따라 결과가 달라지는지 확인하는 합성 시연 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>검토 문장</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>기대 처리</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>검증 목적</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>정산 계좌 826-761414-58373로 입금해 주세요.</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>탐지</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>실제 계좌 문맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>주문번호 826-761414-58373의 배송 상태를 확인해 주세요.</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>같은 형식의 주문번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>biz_reg</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>공급사의 사업자등록번호는 988-90-45770입니다.</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>탐지</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>실제 사업자번호 문맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>biz_reg</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>장비 접수번호 988-90-45770을 작업표에 기록했습니다.</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>같은 형식의 접수번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>법인카드 5508-2407-7250-9350로 결제했습니다.</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>탐지</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>실제 카드 문맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>프로모션 쿠폰번호 5508-2407-7250-9350을 등록했습니다.</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>같은 형식의 쿠폰번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>담당자 휴대전화는 010-7421-3856입니다.</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>탐지</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>휴대전화 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>서울 사무실은 02-6201-3482입니다.</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>탐지</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>서울 지역번호 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>경기 물류센터는 031-555-1234입니다.</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>탐지</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>지역번호 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>긴급 연락처는 01074213856입니다.</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>탐지</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>하이픈 없는 번호 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>사업장 주소는 서울특별시 강남구 테헤란로 152 한빛타워 8층입니다.</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>전체 탐지</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>도로명·건물·층</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>반품 주소는 경기도 성남시 분당구 백현동 532-12 푸른마을아파트 104동 1203호입니다.</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>전체 탐지</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>지번·아파트·동·호</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>이번 회의는 강남역에서 진행합니다.</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>일반 장소 hard negative</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:D17"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/sample_data/demo/고객명단.xlsx
+++ b/sample_data/demo/고객명단.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'고객 현황'!$A$5:$H$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'고객 현황'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'탐지 비교'!$A$4:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'탐지 비교'!$A$4:$B$17</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'탐지 비교'!$A$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>배병철</t>
+          <t>김예은</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>전라남도 수원시 장안구 삼성5가 706-18</t>
+          <t>전북특별자치도 안산시 상록구 삼성거리 504-39 (영진최신동)</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>김명숙</t>
+          <t>이현정</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>충청북도 춘천시 선릉4로 539 (현준김마을)</t>
+          <t>경상북도 파주시 테헤란가 779</t>
         </is>
       </c>
       <c r="G7" s="12" t="n">
@@ -739,7 +739,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>김수진</t>
+          <t>이정순</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>세종특별자치시 강서구 삼성8길 451-99 (성수김윤읍)</t>
+          <t>전북특별자치도 횡성군 도산대0길 172-83 (영일박리)</t>
         </is>
       </c>
       <c r="G8" s="8" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>임건우</t>
+          <t>안영순</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>전북특별자치도 용인시 기흥구 서초대가 893</t>
+          <t>경기도 가평군 오금387길 209-92 (미영김박읍)</t>
         </is>
       </c>
       <c r="G9" s="12" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>류선영</t>
+          <t>이숙자</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>서울특별시 금천구 봉은사로 579-79</t>
+          <t>광주광역시 구로구 서초중앙18길 850 (경숙박강동)</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>김미정</t>
+          <t>허현숙</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>부산광역시 서대문구 반포대3가 287</t>
+          <t>경상남도 증평군 잠실35가 지하962</t>
         </is>
       </c>
       <c r="G11" s="12" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>김영일</t>
+          <t>이성호</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>인천광역시 동대문구 봉은사로 980</t>
+          <t>강원특별자치도 안산시 영동대39로 348-86</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>엄유진</t>
+          <t>이미정</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>대구광역시 강남구 석촌호수4거리 772</t>
+          <t>부산광역시 강서구 논현08거리 지하235</t>
         </is>
       </c>
       <c r="G13" s="12" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>김하윤</t>
+          <t>이지아</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>제주특별자치도 청주시 청원구 테헤란가 467-57</t>
+          <t>경상남도 철원군 가락3가 287</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>이경수</t>
+          <t>노재호</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>울산광역시 금천구 압구정길 441-18 (중수주읍)</t>
+          <t>광주광역시 용산구 잠실01거리 122 (서연이박면)</t>
         </is>
       </c>
       <c r="G15" s="12" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>김선영</t>
+          <t>이정희</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>충청북도 김포시 양재천거리 377 (정순김리)</t>
+          <t>세종특별자치시 양천구 석촌호수길 581 (채원윤손리)</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>김옥순</t>
+          <t>이진우</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>경상남도 보은군 압구정거리 328</t>
+          <t>대구광역시 중랑구 학동거리 지하175 (혜진김김동)</t>
         </is>
       </c>
       <c r="G17" s="12" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>박성훈</t>
+          <t>김수민</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>경상북도 양구군 반포대로 993 (현준정마을)</t>
+          <t>세종특별자치시 강북구 선릉가 972-91</t>
         </is>
       </c>
       <c r="G18" s="8" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>강수빈</t>
+          <t>김진호</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>충청북도 부여군 강남대8가 지하984 (미정이윤리)</t>
+          <t>광주광역시 중랑구 테헤란가 641 (숙자김강면)</t>
         </is>
       </c>
       <c r="G19" s="12" t="n">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>황상호</t>
+          <t>안수빈</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>광주광역시 송파구 개포길 834 (진우하동)</t>
+          <t>서울특별시 서초구 개포로 35-95 (윤서최마을)</t>
         </is>
       </c>
       <c r="G20" s="8" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>이재현</t>
+          <t>김상호</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>강원특별자치도 안양시 만안구 강남대706거리 지하459 (진호김황마을)</t>
+          <t>강원특별자치도 수원시 백제고분430거리 1</t>
         </is>
       </c>
       <c r="G21" s="12" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>김영길</t>
+          <t>백민석</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>세종특별자치시 강남구 봉은사7로 지하987</t>
+          <t>대전광역시 금천구 잠실6길 740 (영일김김동)</t>
         </is>
       </c>
       <c r="G22" s="8" t="n">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>김건우</t>
+          <t>이영길</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>인천광역시 중랑구 영동대71가 999-10 (상철박마을)</t>
+          <t>전북특별자치도 괴산군 석촌호수로 790-73 (서영하면)</t>
         </is>
       </c>
       <c r="G23" s="12" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>윤경희</t>
+          <t>한지혜</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>대전광역시 성북구 봉은사거리 321-55</t>
+          <t>충청북도 군포시 언주7가 90 (서영박면)</t>
         </is>
       </c>
       <c r="G24" s="8" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>박예지</t>
+          <t>최은서</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>부산광역시 중랑구 가락83길 975</t>
+          <t>강원특별자치도 군포시 도산대27가 320-26</t>
         </is>
       </c>
       <c r="G25" s="12" t="n">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>김승민</t>
+          <t>김영호</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>인천광역시 도봉구 백제고분로 527 (경수이동)</t>
+          <t>경상남도 용인시 처인구 언주거리 658 (민수김리)</t>
         </is>
       </c>
       <c r="G26" s="8" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>김채원</t>
+          <t>이미정</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>부산광역시 종로구 오금2거리 199 (경희정마을)</t>
+          <t>대전광역시 강남구 서초중앙거리 329-19</t>
         </is>
       </c>
       <c r="G27" s="12" t="n">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>김정순</t>
+          <t>허재현</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>부산광역시 도봉구 논현거리 612 (지우김한리)</t>
+          <t>대전광역시 남구 서초대가 354 (민준김김읍)</t>
         </is>
       </c>
       <c r="G28" s="8" t="n">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>심상훈</t>
+          <t>김하은</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>대전광역시 강북구 논현가 546</t>
+          <t>서울특별시 동작구 잠실길 689</t>
         </is>
       </c>
       <c r="G29" s="12" t="n">
@@ -1929,26 +1929,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>개인정보 탐지와 오탐 비교</t>
+          <t>개인정보 검토 문장</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>동일한 번호 형식도 문맥에 따라 결과가 달라지는지 확인하는 합성 시연 데이터</t>
+          <t>문맥이 서로 다른 합성 시연 문장</t>
         </is>
       </c>
     </row>
@@ -1963,16 +1961,6 @@
           <t>검토 문장</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>기대 처리</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>검증 목적</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
@@ -1982,17 +1970,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>정산 계좌 826-761414-58373로 입금해 주세요.</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
-        <is>
-          <t>탐지</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>실제 계좌 문맥</t>
+          <t>정산 계좌 917-492-4135637로 입금해 주세요.</t>
         </is>
       </c>
     </row>
@@ -2004,17 +1982,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>주문번호 826-761414-58373의 배송 상태를 확인해 주세요.</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>같은 형식의 주문번호</t>
+          <t>주문번호 917-492-4135637의 배송 상태를 확인해 주세요.</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1994,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>공급사의 사업자등록번호는 988-90-45770입니다.</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="inlineStr">
-        <is>
-          <t>탐지</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>실제 사업자번호 문맥</t>
+          <t>공급사의 사업자등록번호는 879-89-27943입니다.</t>
         </is>
       </c>
     </row>
@@ -2048,17 +2006,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>장비 접수번호 988-90-45770을 작업표에 기록했습니다.</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>같은 형식의 접수번호</t>
+          <t>장비 접수번호 879-89-27943을 작업표에 기록했습니다.</t>
         </is>
       </c>
     </row>
@@ -2070,17 +2018,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>법인카드 5508-2407-7250-9350로 결제했습니다.</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>탐지</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>실제 카드 문맥</t>
+          <t>법인카드 5006-4632-7185-3874로 결제했습니다.</t>
         </is>
       </c>
     </row>
@@ -2092,17 +2030,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>프로모션 쿠폰번호 5508-2407-7250-9350을 등록했습니다.</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>같은 형식의 쿠폰번호</t>
+          <t>프로모션 쿠폰번호 5006-4632-7185-3874을 등록했습니다.</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2045,6 @@
           <t>담당자 휴대전화는 010-7421-3856입니다.</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
-        <is>
-          <t>탐지</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>휴대전화 규칙</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
@@ -2139,16 +2057,6 @@
           <t>서울 사무실은 02-6201-3482입니다.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>탐지</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>서울 지역번호 규칙</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
@@ -2161,16 +2069,6 @@
           <t>경기 물류센터는 031-555-1234입니다.</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
-        <is>
-          <t>탐지</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>지역번호 규칙</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
@@ -2183,16 +2081,6 @@
           <t>긴급 연락처는 01074213856입니다.</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>탐지</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>하이픈 없는 번호 규칙</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
@@ -2205,16 +2093,6 @@
           <t>사업장 주소는 서울특별시 강남구 테헤란로 152 한빛타워 8층입니다.</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>전체 탐지</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>도로명·건물·층</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -2227,16 +2105,6 @@
           <t>반품 주소는 경기도 성남시 분당구 백현동 532-12 푸른마을아파트 104동 1203호입니다.</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>전체 탐지</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>지번·아파트·동·호</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
@@ -2249,22 +2117,12 @@
           <t>이번 회의는 강남역에서 진행합니다.</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>일반 장소 hard negative</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D17"/>
+  <autoFilter ref="A4:B17"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>

--- a/sample_data/demo/고객명단.xlsx
+++ b/sample_data/demo/고객명단.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>김예은</t>
+          <t>배병철</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>전북특별자치도 안산시 상록구 삼성거리 504-39 (영진최신동)</t>
+          <t>전라남도 수원시 장안구 삼성5가 706-18</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>이현정</t>
+          <t>김명숙</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>경상북도 파주시 테헤란가 779</t>
+          <t>충청북도 춘천시 선릉4로 539 (현준김마을)</t>
         </is>
       </c>
       <c r="G7" s="12" t="n">
@@ -739,7 +739,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>이정순</t>
+          <t>김수진</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>전북특별자치도 횡성군 도산대0길 172-83 (영일박리)</t>
+          <t>세종특별자치시 강서구 삼성8길 451-99 (성수김윤읍)</t>
         </is>
       </c>
       <c r="G8" s="8" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>안영순</t>
+          <t>임건우</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>경기도 가평군 오금387길 209-92 (미영김박읍)</t>
+          <t>전북특별자치도 용인시 기흥구 서초대가 893</t>
         </is>
       </c>
       <c r="G9" s="12" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>이숙자</t>
+          <t>류선영</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>광주광역시 구로구 서초중앙18길 850 (경숙박강동)</t>
+          <t>서울특별시 금천구 봉은사로 579-79</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>허현숙</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>경상남도 증평군 잠실35가 지하962</t>
+          <t>부산광역시 서대문구 반포대3가 287</t>
         </is>
       </c>
       <c r="G11" s="12" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>이성호</t>
+          <t>김영일</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>강원특별자치도 안산시 영동대39로 348-86</t>
+          <t>인천광역시 동대문구 봉은사로 980</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>이미정</t>
+          <t>엄유진</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>부산광역시 강서구 논현08거리 지하235</t>
+          <t>대구광역시 강남구 석촌호수4거리 772</t>
         </is>
       </c>
       <c r="G13" s="12" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>이지아</t>
+          <t>김하윤</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>경상남도 철원군 가락3가 287</t>
+          <t>제주특별자치도 청주시 청원구 테헤란가 467-57</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>노재호</t>
+          <t>이경수</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 용산구 잠실01거리 122 (서연이박면)</t>
+          <t>울산광역시 금천구 압구정길 441-18 (중수주읍)</t>
         </is>
       </c>
       <c r="G15" s="12" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>이정희</t>
+          <t>김선영</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>세종특별자치시 양천구 석촌호수길 581 (채원윤손리)</t>
+          <t>충청북도 김포시 양재천거리 377 (정순김리)</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>이진우</t>
+          <t>김옥순</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>대구광역시 중랑구 학동거리 지하175 (혜진김김동)</t>
+          <t>경상남도 보은군 압구정거리 328</t>
         </is>
       </c>
       <c r="G17" s="12" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>김수민</t>
+          <t>박성훈</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>세종특별자치시 강북구 선릉가 972-91</t>
+          <t>경상북도 양구군 반포대로 993 (현준정마을)</t>
         </is>
       </c>
       <c r="G18" s="8" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>김진호</t>
+          <t>강수빈</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 중랑구 테헤란가 641 (숙자김강면)</t>
+          <t>충청북도 부여군 강남대8가 지하984 (미정이윤리)</t>
         </is>
       </c>
       <c r="G19" s="12" t="n">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>안수빈</t>
+          <t>황상호</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 개포로 35-95 (윤서최마을)</t>
+          <t>광주광역시 송파구 개포길 834 (진우하동)</t>
         </is>
       </c>
       <c r="G20" s="8" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>김상호</t>
+          <t>이재현</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>강원특별자치도 수원시 백제고분430거리 1</t>
+          <t>강원특별자치도 안양시 만안구 강남대706거리 지하459 (진호김황마을)</t>
         </is>
       </c>
       <c r="G21" s="12" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>백민석</t>
+          <t>김영길</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>대전광역시 금천구 잠실6길 740 (영일김김동)</t>
+          <t>세종특별자치시 강남구 봉은사7로 지하987</t>
         </is>
       </c>
       <c r="G22" s="8" t="n">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>이영길</t>
+          <t>김건우</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>전북특별자치도 괴산군 석촌호수로 790-73 (서영하면)</t>
+          <t>인천광역시 중랑구 영동대71가 999-10 (상철박마을)</t>
         </is>
       </c>
       <c r="G23" s="12" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>한지혜</t>
+          <t>윤경희</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>충청북도 군포시 언주7가 90 (서영박면)</t>
+          <t>대전광역시 성북구 봉은사거리 321-55</t>
         </is>
       </c>
       <c r="G24" s="8" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>최은서</t>
+          <t>박예지</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>강원특별자치도 군포시 도산대27가 320-26</t>
+          <t>부산광역시 중랑구 가락83길 975</t>
         </is>
       </c>
       <c r="G25" s="12" t="n">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>김영호</t>
+          <t>김승민</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>경상남도 용인시 처인구 언주거리 658 (민수김리)</t>
+          <t>인천광역시 도봉구 백제고분로 527 (경수이동)</t>
         </is>
       </c>
       <c r="G26" s="8" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>이미정</t>
+          <t>김채원</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>대전광역시 강남구 서초중앙거리 329-19</t>
+          <t>부산광역시 종로구 오금2거리 199 (경희정마을)</t>
         </is>
       </c>
       <c r="G27" s="12" t="n">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>허재현</t>
+          <t>김정순</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>대전광역시 남구 서초대가 354 (민준김김읍)</t>
+          <t>부산광역시 도봉구 논현거리 612 (지우김한리)</t>
         </is>
       </c>
       <c r="G28" s="8" t="n">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>김하은</t>
+          <t>심상훈</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>서울특별시 동작구 잠실길 689</t>
+          <t>대전광역시 강북구 논현가 546</t>
         </is>
       </c>
       <c r="G29" s="12" t="n">
@@ -1621,7 +1621,7 @@
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C블루웨이브 솔루션  |  합성 데모 문서&amp;RPage &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;C블루웨이브 솔루션  |  docX-ray 합성 데모 문서&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>InfoGuard의 개인정보 탐지와 마스킹 기능을 시연하기 위한 합성 고객명단</t>
+          <t>docX-ray의 개인정보 탐지와 마스킹 기능을 시연하기 위한 합성 고객명단</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>정산 계좌 917-492-4135637로 입금해 주세요.</t>
+          <t>정산 계좌 8267-614-145837로 입금해 주세요.</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>주문번호 917-492-4135637의 배송 상태를 확인해 주세요.</t>
+          <t>주문번호 8267-614-145837의 배송 상태를 확인해 주세요.</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>공급사의 사업자등록번호는 879-89-27943입니다.</t>
+          <t>공급사의 사업자등록번호는 398-89-04572입니다.</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>장비 접수번호 879-89-27943을 작업표에 기록했습니다.</t>
+          <t>장비 접수번호 398-89-04572을 작업표에 기록했습니다.</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>법인카드 5006-4632-7185-3874로 결제했습니다.</t>
+          <t>법인카드 5750-8240-7725-0938로 결제했습니다.</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>프로모션 쿠폰번호 5006-4632-7185-3874을 등록했습니다.</t>
+          <t>프로모션 쿠폰번호 5750-8240-7725-0938을 등록했습니다.</t>
         </is>
       </c>
     </row>
